--- a/发布历史(from_2025.10).xlsx
+++ b/发布历史(from_2025.10).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="政策历史" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="政策历史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/发布历史(from_2025.10).xlsx
+++ b/发布历史(from_2025.10).xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5344,6 +5344,28 @@
       <c r="D223" s="2" t="inlineStr">
         <is>
           <t>http://www.customs.gov.cn/customs/2025-11/04/article_2025122718034589880.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>海关总署公告2026年第154号（关于进口智利鲜食水果植物检疫补充要求的公告）</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>最新文件</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/2026-10/30/article_2026103010280963186.html</t>
         </is>
       </c>
     </row>
@@ -5571,6 +5593,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId223"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/发布历史(from_2025.10).xlsx
+++ b/发布历史(from_2025.10).xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5366,6 +5366,28 @@
       <c r="D224" s="2" t="inlineStr">
         <is>
           <t>http://www.customs.gov.cn/customs/2026-10/30/article_2026103010280963186.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>海关总署公告2026年第155号（关于公布《中华人民共和国海关〈中华人民共和国政府与秘鲁共和国政府自由贸易协定〉项下经修订的进出口货物原产地管理办法》的公告）</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>最新文件</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/2026-10/30/article_2026103020541861461.html</t>
         </is>
       </c>
     </row>
@@ -5594,6 +5616,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId224"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
